--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -5,16 +5,26 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f19fb36a3f97524f/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f19fb36a3f97524f/Desktop/Dmart_Sales/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A783F98-E7B9-48F0-B880-BE381BE614FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="8_{5A783F98-E7B9-48F0-B880-BE381BE614FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{740D5C0C-9A3D-4A48-A569-2FA9CE494CA2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2516AB57-94B7-483D-B023-2E9B28841551}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="consolidate" sheetId="7" r:id="rId7"/>
   </sheets>
+  <definedNames>
+    <definedName name="Discount">Table1[[#All],[Discount]]</definedName>
+    <definedName name="unit">Table1[Discount]</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,8 +45,45 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="33">
   <si>
     <t>Unit Price</t>
   </si>
@@ -90,16 +137,67 @@
   </si>
   <si>
     <t>rounddown</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>su</t>
+  </si>
+  <si>
+    <t>JAN</t>
+  </si>
+  <si>
+    <t>FEB</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>APR</t>
+  </si>
+  <si>
+    <t>Person A</t>
+  </si>
+  <si>
+    <t>Person B</t>
+  </si>
+  <si>
+    <t>Person C</t>
+  </si>
+  <si>
+    <t>Person D</t>
+  </si>
+  <si>
+    <t>Column4</t>
+  </si>
+  <si>
+    <t>Column5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -142,6 +240,142 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>13</v>
+    <v>7</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{974077F8-D54E-46F5-AB46-6FDE880E58D7}" name="Table1" displayName="Table1" ref="A1:E13" totalsRowShown="0">
+  <autoFilter ref="A1:E13" xr:uid="{974077F8-D54E-46F5-AB46-6FDE880E58D7}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{91B3E4CE-44DF-4BB4-8CF7-CD7C1DD5D868}" name="Discount"/>
+    <tableColumn id="2" xr3:uid="{D0DB1111-2B26-4DD8-9501-06704CA58645}" name="0.25"/>
+    <tableColumn id="3" xr3:uid="{A1B579C5-9EDF-40A8-B938-95B6AC96E193}" name="Column1"/>
+    <tableColumn id="4" xr3:uid="{F3555D1F-4AFF-49FE-8B05-635A42133E1E}" name="Column2">
+      <calculatedColumnFormula>C2*$B$1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{F5FCEC11-7495-4729-A743-EEE23E0958E6}" name="Column3">
+      <calculatedColumnFormula>C2-D2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BC544315-AC5E-4AB8-A178-8695D8390A7E}" name="Table13" displayName="Table13" ref="I9:M21" totalsRowShown="0">
+  <autoFilter ref="I9:M21" xr:uid="{BC544315-AC5E-4AB8-A178-8695D8390A7E}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{A1DEC77E-DC49-442C-B92D-7582761F1217}" name="Discount"/>
+    <tableColumn id="2" xr3:uid="{CD3084CB-2487-4C52-85D7-4018D1A85872}" name="0.25"/>
+    <tableColumn id="3" xr3:uid="{C0DBC02E-61E2-4714-8857-0CA8C660A7CC}" name="Column1"/>
+    <tableColumn id="4" xr3:uid="{E326D7F6-FB9E-4AC6-8801-29C9AF558984}" name="Column2">
+      <calculatedColumnFormula>K10*$B$1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{AE18D2C4-8ED4-4179-BFC2-1CCF3CEC9335}" name="Column3">
+      <calculatedColumnFormula>K10-L10</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0FD6004B-F262-4C0C-A3EB-2C9A5E65A4E1}" name="Table4" displayName="Table4" ref="I5:I6" insertRow="1" totalsRowShown="0">
+  <autoFilter ref="I5:I6" xr:uid="{0FD6004B-F262-4C0C-A3EB-2C9A5E65A4E1}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{50073A97-1EFA-477B-9629-871D83CD380C}" name="Column1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{DB081821-3717-4564-835A-D1180EE37727}" name="Table5" displayName="Table5" ref="A1:E5" totalsRowShown="0">
+  <autoFilter ref="A1:E5" xr:uid="{DB081821-3717-4564-835A-D1180EE37727}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{EC58A048-723D-493C-9E6C-C57120597E7D}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{AAD0CE84-3494-4F28-91C9-59036D31F0B5}" name="JAN"/>
+    <tableColumn id="3" xr3:uid="{E2CA7CC4-6A3C-4441-858F-BF4FFD0B93DE}" name="FEB"/>
+    <tableColumn id="4" xr3:uid="{D4FE5AF9-58BC-42D0-8ABC-1B147C50F310}" name="MAR"/>
+    <tableColumn id="5" xr3:uid="{26C1EAD6-8ACA-4CA1-8484-A355922A42E8}" name="APR"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BC66BE43-589F-41A0-BFD7-0B1A8A289D8C}" name="Table3" displayName="Table3" ref="N16:R21" totalsRowShown="0">
+  <autoFilter ref="N16:R21" xr:uid="{BC66BE43-589F-41A0-BFD7-0B1A8A289D8C}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{86C466F2-54EF-45ED-9F1C-DB6E83B3F12A}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{63DBD2E6-FA00-4741-8B75-B4050D410A96}" name="Column2"/>
+    <tableColumn id="3" xr3:uid="{AA1BF894-A7DF-4410-8679-DDCBA44EB3B5}" name="Column3"/>
+    <tableColumn id="4" xr3:uid="{83D74792-C346-40ED-AA52-4F6694B76D27}" name="Column4"/>
+    <tableColumn id="5" xr3:uid="{3C0E922A-E546-4BE8-92D5-F06D132A43DE}" name="Column5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,7 +698,8 @@
   <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="9.453125" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" customWidth="1"/>
     <col min="4" max="4" width="13.54296875" customWidth="1"/>
     <col min="5" max="5" width="13.26953125" customWidth="1"/>
   </cols>
@@ -473,8 +708,17 @@
       <c r="A1" t="s">
         <v>3</v>
       </c>
-      <c r="B1">
-        <v>0.25</v>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
@@ -552,23 +796,23 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <f>$I4*J$3</f>
+        <f t="shared" ref="J4:N8" si="3">$I4*J$3</f>
         <v>10</v>
       </c>
       <c r="K4">
-        <f>$I4*K$3</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="L4">
-        <f>$I4*L$3</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="M4">
-        <f>$I4*M$3</f>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="N4">
-        <f>$I4*N$3</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
@@ -595,23 +839,23 @@
         <v>20</v>
       </c>
       <c r="J5">
-        <f>$I5*J$3</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="K5">
-        <f>$I5*K$3</f>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="L5">
-        <f>$I5*L$3</f>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="M5">
-        <f>$I5*M$3</f>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="N5">
-        <f>$I5*N$3</f>
+        <f t="shared" si="3"/>
         <v>100</v>
       </c>
     </row>
@@ -638,23 +882,23 @@
         <v>30</v>
       </c>
       <c r="J6">
-        <f>$I6*J$3</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="K6">
-        <f>$I6*K$3</f>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="L6">
-        <f>$I6*L$3</f>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="M6">
-        <f>$I6*M$3</f>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
       <c r="N6">
-        <f>$I6*N$3</f>
+        <f t="shared" si="3"/>
         <v>150</v>
       </c>
     </row>
@@ -681,23 +925,23 @@
         <v>40</v>
       </c>
       <c r="J7">
-        <f>$I7*J$3</f>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="K7">
-        <f>$I7*K$3</f>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="L7">
-        <f>$I7*L$3</f>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
       <c r="M7">
-        <f>$I7*M$3</f>
+        <f t="shared" si="3"/>
         <v>160</v>
       </c>
       <c r="N7">
-        <f>$I7*N$3</f>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
     </row>
@@ -724,23 +968,23 @@
         <v>50</v>
       </c>
       <c r="J8">
-        <f>$I8*J$3</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="K8">
-        <f>$I8*K$3</f>
+        <f t="shared" si="3"/>
         <v>100</v>
       </c>
       <c r="L8">
-        <f>$I8*L$3</f>
+        <f t="shared" si="3"/>
         <v>150</v>
       </c>
       <c r="M8">
-        <f>$I8*M$3</f>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="N8">
-        <f>$I8*N$3</f>
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
     </row>
@@ -857,6 +1101,10 @@
         <f t="shared" si="2"/>
         <v>7.5</v>
       </c>
+      <c r="G14">
+        <f>SUM(unit,Table1[[#Headers],[0.25]])</f>
+        <v>38758</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
@@ -866,6 +1114,10 @@
         <f>COUNTA(C3:C12)</f>
         <v>10</v>
       </c>
+      <c r="G15">
+        <f>SUM(unit)</f>
+        <v>38758</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
@@ -950,5 +1202,1360 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C27B6B8-3E83-4015-AEFF-39906075250D}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="9" max="9" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" t="str" cm="1">
+        <f t="array" ref="A1:A12">unit</f>
+        <v>Unit Price</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1">
+        <f>SUM(Discount)</f>
+        <v>38758</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>5675</v>
+      </c>
+      <c r="D2" t="e" vm="1">
+        <f>_xleta.DISC</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>3621</v>
+      </c>
+      <c r="D3" t="str" cm="1">
+        <f t="array" ref="D3:D15">Discount</f>
+        <v>Discount</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2633</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Unit Price</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2575</v>
+      </c>
+      <c r="D5">
+        <v>5675</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>4631</v>
+      </c>
+      <c r="D6">
+        <v>3621</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>3779</v>
+      </c>
+      <c r="D7">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5085</v>
+      </c>
+      <c r="D8">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>4248</v>
+      </c>
+      <c r="D9">
+        <v>4631</v>
+      </c>
+      <c r="I9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1655</v>
+      </c>
+      <c r="D10">
+        <v>3779</v>
+      </c>
+      <c r="I10" t="s">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>2</v>
+      </c>
+      <c r="L10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>4856</v>
+      </c>
+      <c r="D11">
+        <v>5085</v>
+      </c>
+      <c r="I11">
+        <v>5675</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+      <c r="K11">
+        <f>I11*J11</f>
+        <v>56750</v>
+      </c>
+      <c r="L11" t="e">
+        <f>K11*$B$1</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M11" t="e">
+        <f>K11-L11</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>4248</v>
+      </c>
+      <c r="I12">
+        <v>3621</v>
+      </c>
+      <c r="J12">
+        <v>9</v>
+      </c>
+      <c r="K12">
+        <f t="shared" ref="K12:K20" si="0">I12*J12</f>
+        <v>32589</v>
+      </c>
+      <c r="L12" t="e">
+        <f t="shared" ref="L12:L21" si="1">K12*$B$1</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M12" t="e">
+        <f t="shared" ref="M12:M21" si="2">K12-L12</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="D13">
+        <v>1655</v>
+      </c>
+      <c r="I13">
+        <v>2633</v>
+      </c>
+      <c r="J13">
+        <v>7</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>18431</v>
+      </c>
+      <c r="L13" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M13" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="D14">
+        <v>4856</v>
+      </c>
+      <c r="I14">
+        <v>2575</v>
+      </c>
+      <c r="J14">
+        <v>10</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>25750</v>
+      </c>
+      <c r="L14" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M14" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>4631</v>
+      </c>
+      <c r="J15">
+        <v>5</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="0"/>
+        <v>23155</v>
+      </c>
+      <c r="L15" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M15" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I16">
+        <v>3779</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="0"/>
+        <v>11337</v>
+      </c>
+      <c r="L16" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M16" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="9:13" x14ac:dyDescent="0.35">
+      <c r="I17">
+        <v>5085</v>
+      </c>
+      <c r="J17">
+        <v>9</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>45765</v>
+      </c>
+      <c r="L17" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M17" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="9:13" x14ac:dyDescent="0.35">
+      <c r="I18">
+        <v>4248</v>
+      </c>
+      <c r="J18">
+        <v>8</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="0"/>
+        <v>33984</v>
+      </c>
+      <c r="L18" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M18" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="9:13" x14ac:dyDescent="0.35">
+      <c r="I19">
+        <v>1655</v>
+      </c>
+      <c r="J19">
+        <v>5</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="0"/>
+        <v>8275</v>
+      </c>
+      <c r="L19" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M19" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="20" spans="9:13" x14ac:dyDescent="0.35">
+      <c r="I20">
+        <v>4856</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="0"/>
+        <v>14568</v>
+      </c>
+      <c r="L20" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M20" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" spans="9:13" x14ac:dyDescent="0.35">
+      <c r="J21" t="s">
+        <v>6</v>
+      </c>
+      <c r="K21">
+        <f>SUM(K11:K20)</f>
+        <v>270604</v>
+      </c>
+      <c r="L21" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M21" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D821622A-A9E6-4E62-97C3-4E917CA6257B}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <f t="shared" ref="B2:F6" ca="1" si="0">$I2*B$3</f>
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="E2">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="F2">
+        <f t="shared" ca="1" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ca="1" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ca="1" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ca="1" si="0"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>30</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ca="1" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ca="1" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ca="1" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="F4">
+        <f t="shared" ca="1" si="0"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ca="1" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D5">
+        <f t="shared" ca="1" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ca="1" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="F5">
+        <f t="shared" ca="1" si="0"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>50</v>
+      </c>
+      <c r="B6">
+        <f t="shared" ca="1" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ca="1" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ca="1" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="E6">
+        <f t="shared" ca="1" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="F6">
+        <f t="shared" ca="1" si="0"/>
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92FD34AD-8689-49B3-86CA-AA5A300AA926}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F27DB98-E71A-4192-AE5A-E90A0877F9EA}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2">
+        <v>739</v>
+      </c>
+      <c r="C2">
+        <v>324</v>
+      </c>
+      <c r="D2">
+        <v>2414</v>
+      </c>
+      <c r="E2">
+        <v>5457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
+        <v>678</v>
+      </c>
+      <c r="C3">
+        <v>8887</v>
+      </c>
+      <c r="D3">
+        <v>8920</v>
+      </c>
+      <c r="E3">
+        <v>4358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4">
+        <v>432</v>
+      </c>
+      <c r="C4">
+        <v>5776</v>
+      </c>
+      <c r="D4">
+        <v>3457</v>
+      </c>
+      <c r="E4">
+        <v>9654</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5">
+        <v>544</v>
+      </c>
+      <c r="C5">
+        <v>6567</v>
+      </c>
+      <c r="D5">
+        <v>4567</v>
+      </c>
+      <c r="E5">
+        <v>7898</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3BF5335-0734-43BC-9D9B-F2FE4578C1B3}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.453125" customWidth="1"/>
+    <col min="9" max="9" width="10.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2">
+        <v>739</v>
+      </c>
+      <c r="C2">
+        <v>324</v>
+      </c>
+      <c r="D2">
+        <v>2414</v>
+      </c>
+      <c r="E2">
+        <v>5457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
+        <v>678</v>
+      </c>
+      <c r="C3">
+        <v>8887</v>
+      </c>
+      <c r="D3">
+        <v>8920</v>
+      </c>
+      <c r="E3">
+        <v>4358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4">
+        <v>432</v>
+      </c>
+      <c r="C4">
+        <v>5776</v>
+      </c>
+      <c r="D4">
+        <v>3457</v>
+      </c>
+      <c r="E4">
+        <v>9654</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5">
+        <v>544</v>
+      </c>
+      <c r="C5">
+        <v>6567</v>
+      </c>
+      <c r="D5">
+        <v>4567</v>
+      </c>
+      <c r="E5">
+        <v>7898</v>
+      </c>
+      <c r="I5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF7552E3-18B2-4F4F-8898-31232630D347}">
+  <dimension ref="A1:R48"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="3" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
+    <col min="9" max="9" width="10.26953125" customWidth="1"/>
+    <col min="10" max="10" width="6.90625" customWidth="1"/>
+    <col min="14" max="18" width="10.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="B2">
+        <f>Sheet3!$B$2</f>
+        <v>739</v>
+      </c>
+      <c r="C2">
+        <f>Sheet3!$C$2</f>
+        <v>324</v>
+      </c>
+      <c r="D2">
+        <f>Sheet3!$D$2</f>
+        <v>2414</v>
+      </c>
+      <c r="E2">
+        <f>Sheet3!$E$2</f>
+        <v>5457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="B3">
+        <f>Sheet6!$B$2</f>
+        <v>739</v>
+      </c>
+      <c r="C3">
+        <f>Sheet6!$C$2</f>
+        <v>324</v>
+      </c>
+      <c r="D3">
+        <f>Sheet6!$D$2</f>
+        <v>2414</v>
+      </c>
+      <c r="E3">
+        <f>Sheet6!$E$2</f>
+        <v>5457</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4">
+        <f>SUM(B2:B3)</f>
+        <v>1478</v>
+      </c>
+      <c r="C4">
+        <f>SUM(C2:C3)</f>
+        <v>648</v>
+      </c>
+      <c r="D4">
+        <f>SUM(D2:D3)</f>
+        <v>4828</v>
+      </c>
+      <c r="E4">
+        <f>SUM(E2:E3)</f>
+        <v>10914</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="B5">
+        <f>Sheet3!$B$3</f>
+        <v>678</v>
+      </c>
+      <c r="C5">
+        <f>Sheet3!$C$3</f>
+        <v>8887</v>
+      </c>
+      <c r="D5">
+        <f>Sheet3!$D$3</f>
+        <v>8920</v>
+      </c>
+      <c r="E5">
+        <f>Sheet3!$E$3</f>
+        <v>4358</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="B6">
+        <f>Sheet6!$B$3</f>
+        <v>678</v>
+      </c>
+      <c r="C6">
+        <f>Sheet6!$C$3</f>
+        <v>8887</v>
+      </c>
+      <c r="D6">
+        <f>Sheet6!$D$3</f>
+        <v>8920</v>
+      </c>
+      <c r="E6">
+        <f>Sheet6!$E$3</f>
+        <v>4358</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7">
+        <f>SUM(B5:B6)</f>
+        <v>1356</v>
+      </c>
+      <c r="C7">
+        <f>SUM(C5:C6)</f>
+        <v>17774</v>
+      </c>
+      <c r="D7">
+        <f>SUM(D5:D6)</f>
+        <v>17840</v>
+      </c>
+      <c r="E7">
+        <f>SUM(E5:E6)</f>
+        <v>8716</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="B8">
+        <f>Sheet3!$B$4</f>
+        <v>432</v>
+      </c>
+      <c r="C8">
+        <f>Sheet3!$C$4</f>
+        <v>5776</v>
+      </c>
+      <c r="D8">
+        <f>Sheet3!$D$4</f>
+        <v>3457</v>
+      </c>
+      <c r="E8">
+        <f>Sheet3!$E$4</f>
+        <v>9654</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="B9">
+        <f>Sheet6!$B$4</f>
+        <v>432</v>
+      </c>
+      <c r="C9">
+        <f>Sheet6!$C$4</f>
+        <v>5776</v>
+      </c>
+      <c r="D9">
+        <f>Sheet6!$D$4</f>
+        <v>3457</v>
+      </c>
+      <c r="E9">
+        <f>Sheet6!$E$4</f>
+        <v>9654</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10">
+        <f>SUM(B8:B9)</f>
+        <v>864</v>
+      </c>
+      <c r="C10">
+        <f>SUM(C8:C9)</f>
+        <v>11552</v>
+      </c>
+      <c r="D10">
+        <f>SUM(D8:D9)</f>
+        <v>6914</v>
+      </c>
+      <c r="E10">
+        <f>SUM(E8:E9)</f>
+        <v>19308</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="B11">
+        <f>Sheet3!$B$5</f>
+        <v>544</v>
+      </c>
+      <c r="C11">
+        <f>Sheet3!$C$5</f>
+        <v>6567</v>
+      </c>
+      <c r="D11">
+        <f>Sheet3!$D$5</f>
+        <v>4567</v>
+      </c>
+      <c r="E11">
+        <f>Sheet3!$E$5</f>
+        <v>7898</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="B12">
+        <f>Sheet6!$B$5</f>
+        <v>544</v>
+      </c>
+      <c r="C12">
+        <f>Sheet6!$C$5</f>
+        <v>6567</v>
+      </c>
+      <c r="D12">
+        <f>Sheet6!$D$5</f>
+        <v>4567</v>
+      </c>
+      <c r="E12">
+        <f>Sheet6!$E$5</f>
+        <v>7898</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13">
+        <f>SUM(B11:B12)</f>
+        <v>1088</v>
+      </c>
+      <c r="C13">
+        <f>SUM(C11:C12)</f>
+        <v>13134</v>
+      </c>
+      <c r="D13">
+        <f>SUM(D11:D12)</f>
+        <v>9134</v>
+      </c>
+      <c r="E13">
+        <f>SUM(E11:E12)</f>
+        <v>15796</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="N16" t="s">
+        <v>19</v>
+      </c>
+      <c r="O16" t="s">
+        <v>20</v>
+      </c>
+      <c r="P16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="6:18" hidden="1" outlineLevel="3" x14ac:dyDescent="0.35">
+      <c r="F21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21">
+        <v>432</v>
+      </c>
+      <c r="H21">
+        <v>5776</v>
+      </c>
+      <c r="I21">
+        <v>3457</v>
+      </c>
+      <c r="J21">
+        <f>Sheet3!$B$2</f>
+        <v>739</v>
+      </c>
+      <c r="K21">
+        <f>Sheet3!$C$2</f>
+        <v>324</v>
+      </c>
+      <c r="L21">
+        <f>Sheet3!$D$2</f>
+        <v>2414</v>
+      </c>
+      <c r="M21">
+        <f>Sheet3!$E$2</f>
+        <v>5457</v>
+      </c>
+      <c r="O21">
+        <v>544</v>
+      </c>
+      <c r="P21">
+        <v>6567</v>
+      </c>
+      <c r="Q21">
+        <v>4567</v>
+      </c>
+      <c r="R21">
+        <v>7898</v>
+      </c>
+    </row>
+    <row r="22" spans="6:18" hidden="1" outlineLevel="3" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="F22" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22">
+        <v>544</v>
+      </c>
+      <c r="H22">
+        <v>6567</v>
+      </c>
+      <c r="I22">
+        <v>4567</v>
+      </c>
+      <c r="J22">
+        <f>Sheet6!$B$2</f>
+        <v>739</v>
+      </c>
+      <c r="K22">
+        <f>Sheet6!$C$2</f>
+        <v>324</v>
+      </c>
+      <c r="L22">
+        <f>Sheet6!$D$2</f>
+        <v>2414</v>
+      </c>
+      <c r="M22">
+        <f>Sheet6!$E$2</f>
+        <v>5457</v>
+      </c>
+    </row>
+    <row r="23" spans="6:18" hidden="1" outlineLevel="2" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="J23">
+        <f>AVERAGE(J21:J22)</f>
+        <v>739</v>
+      </c>
+      <c r="K23">
+        <f>AVERAGE(K21:K22)</f>
+        <v>324</v>
+      </c>
+      <c r="L23">
+        <f>AVERAGE(L21:L22)</f>
+        <v>2414</v>
+      </c>
+      <c r="M23">
+        <f>AVERAGE(M21:M22)</f>
+        <v>5457</v>
+      </c>
+    </row>
+    <row r="24" spans="6:18" hidden="1" outlineLevel="3" x14ac:dyDescent="0.35">
+      <c r="J24">
+        <f>Sheet3!$B$3</f>
+        <v>678</v>
+      </c>
+      <c r="K24">
+        <f>Sheet3!$C$3</f>
+        <v>8887</v>
+      </c>
+      <c r="L24">
+        <f>Sheet3!$D$3</f>
+        <v>8920</v>
+      </c>
+      <c r="M24">
+        <f>Sheet3!$E$3</f>
+        <v>4358</v>
+      </c>
+    </row>
+    <row r="25" spans="6:18" hidden="1" outlineLevel="3" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="J25">
+        <f>Sheet6!$B$3</f>
+        <v>678</v>
+      </c>
+      <c r="K25">
+        <f>Sheet6!$C$3</f>
+        <v>8887</v>
+      </c>
+      <c r="L25">
+        <f>Sheet6!$D$3</f>
+        <v>8920</v>
+      </c>
+      <c r="M25">
+        <f>Sheet6!$E$3</f>
+        <v>4358</v>
+      </c>
+    </row>
+    <row r="26" spans="6:18" hidden="1" outlineLevel="2" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="J26">
+        <f>AVERAGE(J24:J25)</f>
+        <v>678</v>
+      </c>
+      <c r="K26">
+        <f>AVERAGE(K24:K25)</f>
+        <v>8887</v>
+      </c>
+      <c r="L26">
+        <f>AVERAGE(L24:L25)</f>
+        <v>8920</v>
+      </c>
+      <c r="M26">
+        <f>AVERAGE(M24:M25)</f>
+        <v>4358</v>
+      </c>
+    </row>
+    <row r="27" spans="6:18" hidden="1" outlineLevel="3" x14ac:dyDescent="0.35">
+      <c r="J27">
+        <f>Sheet3!$B$4</f>
+        <v>432</v>
+      </c>
+      <c r="K27">
+        <f>Sheet3!$C$4</f>
+        <v>5776</v>
+      </c>
+      <c r="L27">
+        <f>Sheet3!$D$4</f>
+        <v>3457</v>
+      </c>
+      <c r="M27">
+        <f>Sheet3!$E$4</f>
+        <v>9654</v>
+      </c>
+    </row>
+    <row r="28" spans="6:18" hidden="1" outlineLevel="3" x14ac:dyDescent="0.35">
+      <c r="J28">
+        <f>Sheet6!$B$4</f>
+        <v>432</v>
+      </c>
+      <c r="K28">
+        <f>Sheet6!$C$4</f>
+        <v>5776</v>
+      </c>
+      <c r="L28">
+        <f>Sheet6!$D$4</f>
+        <v>3457</v>
+      </c>
+      <c r="M28">
+        <f>Sheet6!$E$4</f>
+        <v>9654</v>
+      </c>
+    </row>
+    <row r="29" spans="6:18" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="J29">
+        <f>AVERAGE(J27:J28)</f>
+        <v>432</v>
+      </c>
+      <c r="K29">
+        <f>AVERAGE(K27:K28)</f>
+        <v>5776</v>
+      </c>
+      <c r="L29">
+        <f>AVERAGE(L27:L28)</f>
+        <v>3457</v>
+      </c>
+      <c r="M29">
+        <f>AVERAGE(M27:M28)</f>
+        <v>9654</v>
+      </c>
+    </row>
+    <row r="30" spans="6:18" hidden="1" outlineLevel="3" x14ac:dyDescent="0.35">
+      <c r="J30">
+        <f>Sheet3!$B$5</f>
+        <v>544</v>
+      </c>
+      <c r="K30">
+        <f>Sheet3!$C$5</f>
+        <v>6567</v>
+      </c>
+      <c r="L30">
+        <f>Sheet3!$D$5</f>
+        <v>4567</v>
+      </c>
+      <c r="M30">
+        <f>Sheet3!$E$5</f>
+        <v>7898</v>
+      </c>
+    </row>
+    <row r="31" spans="6:18" hidden="1" outlineLevel="3" x14ac:dyDescent="0.35">
+      <c r="J31">
+        <f>Sheet6!$B$5</f>
+        <v>544</v>
+      </c>
+      <c r="K31">
+        <f>Sheet6!$C$5</f>
+        <v>6567</v>
+      </c>
+      <c r="L31">
+        <f>Sheet6!$D$5</f>
+        <v>4567</v>
+      </c>
+      <c r="M31">
+        <f>Sheet6!$E$5</f>
+        <v>7898</v>
+      </c>
+    </row>
+    <row r="32" spans="6:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.35">
+      <c r="J32">
+        <f>AVERAGE(J30:J31)</f>
+        <v>544</v>
+      </c>
+      <c r="K32">
+        <f>AVERAGE(K30:K31)</f>
+        <v>6567</v>
+      </c>
+      <c r="L32">
+        <f>AVERAGE(L30:L31)</f>
+        <v>4567</v>
+      </c>
+      <c r="M32">
+        <f>AVERAGE(M30:M31)</f>
+        <v>7898</v>
+      </c>
+    </row>
+    <row r="33" spans="5:9" hidden="1" outlineLevel="2" collapsed="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="5:9" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="5:9" hidden="1" outlineLevel="2" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="5:9" hidden="1" outlineLevel="2" x14ac:dyDescent="0.35"/>
+    <row r="37" spans="5:9" collapsed="1" x14ac:dyDescent="0.35"/>
+    <row r="38" spans="5:9" hidden="1" outlineLevel="2" x14ac:dyDescent="0.35">
+      <c r="E38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38">
+        <v>985.33333333333337</v>
+      </c>
+      <c r="G38">
+        <v>432</v>
+      </c>
+      <c r="H38">
+        <v>3218.6666666666665</v>
+      </c>
+      <c r="I38">
+        <v>7276</v>
+      </c>
+    </row>
+    <row r="39" spans="5:9" hidden="1" outlineLevel="2" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="E39" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39">
+        <v>678</v>
+      </c>
+      <c r="G39">
+        <v>8887</v>
+      </c>
+      <c r="H39">
+        <v>8920</v>
+      </c>
+      <c r="I39">
+        <v>4358</v>
+      </c>
+    </row>
+    <row r="40" spans="5:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="E40" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40">
+        <v>432</v>
+      </c>
+      <c r="G40">
+        <v>5776</v>
+      </c>
+      <c r="H40">
+        <v>3457</v>
+      </c>
+      <c r="I40">
+        <v>9654</v>
+      </c>
+    </row>
+    <row r="41" spans="5:9" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35">
+      <c r="E41" t="s">
+        <v>30</v>
+      </c>
+      <c r="F41">
+        <v>544</v>
+      </c>
+      <c r="G41">
+        <v>6567</v>
+      </c>
+      <c r="H41">
+        <v>4567</v>
+      </c>
+      <c r="I41">
+        <v>7898</v>
+      </c>
+    </row>
+    <row r="42" spans="5:9" collapsed="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="5:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="5:9" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="5:9" collapsed="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="5:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="5:9" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35"/>
+    <row r="48" spans="5:9" collapsed="1" x14ac:dyDescent="0.35"/>
+  </sheetData>
+  <dataConsolidate function="average" leftLabels="1" topLabels="1">
+    <dataRefs count="3">
+      <dataRef ref="A1:E5" sheet="consolidate"/>
+      <dataRef ref="A1:E5" sheet="Sheet3"/>
+      <dataRef ref="A1:E5" sheet="Sheet6"/>
+    </dataRefs>
+  </dataConsolidate>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f19fb36a3f97524f/Desktop/Dmart_Sales/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="8_{5A783F98-E7B9-48F0-B880-BE381BE614FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{740D5C0C-9A3D-4A48-A569-2FA9CE494CA2}"/>
+  <xr:revisionPtr revIDLastSave="280" documentId="8_{5A783F98-E7B9-48F0-B880-BE381BE614FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40A1AF96-7C44-4A4F-B52A-5B1D18ABC00F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2516AB57-94B7-483D-B023-2E9B28841551}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{2516AB57-94B7-483D-B023-2E9B28841551}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet7" sheetId="8" r:id="rId2"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
-    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
-    <sheet name="consolidate" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId5"/>
+    <sheet name="consolidate" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Discount">Table1[[#All],[Discount]]</definedName>
@@ -45,45 +44,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="2">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="2" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="62">
   <si>
     <t>Unit Price</t>
   </si>
@@ -151,9 +113,6 @@
     <t>Column3</t>
   </si>
   <si>
-    <t>su</t>
-  </si>
-  <si>
     <t>JAN</t>
   </si>
   <si>
@@ -182,22 +141,106 @@
   </si>
   <si>
     <t>Column5</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>mumbai</t>
+  </si>
+  <si>
+    <t>pune</t>
+  </si>
+  <si>
+    <t>thane</t>
+  </si>
+  <si>
+    <t>bangalore</t>
+  </si>
+  <si>
+    <t>WholeNumber</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>length</t>
+  </si>
+  <si>
+    <t>vicky</t>
+  </si>
+  <si>
+    <t>bhishamlal</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>department</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Computer</t>
+  </si>
+  <si>
+    <t>Mechanical</t>
+  </si>
+  <si>
+    <t>Civil</t>
+  </si>
+  <si>
+    <t>CSD</t>
+  </si>
+  <si>
+    <t>Ai</t>
+  </si>
+  <si>
+    <t>Sshivam</t>
+  </si>
+  <si>
+    <t>hutufrfi</t>
+  </si>
+  <si>
+    <t>qwertyui</t>
+  </si>
+  <si>
+    <t>aa aaa aaaa</t>
+  </si>
+  <si>
+    <t>b bb bbb</t>
+  </si>
+  <si>
+    <t>cccc cccccc  c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ddd dddd ddddd </t>
+  </si>
+  <si>
+    <t>fS</t>
+  </si>
+  <si>
+    <t>ss</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -211,7 +254,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -219,12 +262,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -246,64 +306,6 @@
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>13</v>
-    <v>7</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="subType" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{974077F8-D54E-46F5-AB46-6FDE880E58D7}" name="Table1" displayName="Table1" ref="A1:E13" totalsRowShown="0">
   <autoFilter ref="A1:E13" xr:uid="{974077F8-D54E-46F5-AB46-6FDE880E58D7}"/>
@@ -323,24 +325,6 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{BC544315-AC5E-4AB8-A178-8695D8390A7E}" name="Table13" displayName="Table13" ref="I9:M21" totalsRowShown="0">
-  <autoFilter ref="I9:M21" xr:uid="{BC544315-AC5E-4AB8-A178-8695D8390A7E}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A1DEC77E-DC49-442C-B92D-7582761F1217}" name="Discount"/>
-    <tableColumn id="2" xr3:uid="{CD3084CB-2487-4C52-85D7-4018D1A85872}" name="0.25"/>
-    <tableColumn id="3" xr3:uid="{C0DBC02E-61E2-4714-8857-0CA8C660A7CC}" name="Column1"/>
-    <tableColumn id="4" xr3:uid="{E326D7F6-FB9E-4AC6-8801-29C9AF558984}" name="Column2">
-      <calculatedColumnFormula>K10*$B$1</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{AE18D2C4-8ED4-4179-BFC2-1CCF3CEC9335}" name="Column3">
-      <calculatedColumnFormula>K10-L10</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0FD6004B-F262-4C0C-A3EB-2C9A5E65A4E1}" name="Table4" displayName="Table4" ref="I5:I6" insertRow="1" totalsRowShown="0">
   <autoFilter ref="I5:I6" xr:uid="{0FD6004B-F262-4C0C-A3EB-2C9A5E65A4E1}"/>
   <tableColumns count="1">
@@ -350,7 +334,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{DB081821-3717-4564-835A-D1180EE37727}" name="Table5" displayName="Table5" ref="A1:E5" totalsRowShown="0">
   <autoFilter ref="A1:E5" xr:uid="{DB081821-3717-4564-835A-D1180EE37727}"/>
   <tableColumns count="5">
@@ -364,7 +348,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{BC66BE43-589F-41A0-BFD7-0B1A8A289D8C}" name="Table3" displayName="Table3" ref="N16:R21" totalsRowShown="0">
   <autoFilter ref="N16:R21" xr:uid="{BC66BE43-589F-41A0-BFD7-0B1A8A289D8C}"/>
   <tableColumns count="5">
@@ -1209,377 +1193,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C27B6B8-3E83-4015-AEFF-39906075250D}">
-  <dimension ref="A1:M21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316AFA1E-338E-4632-BFA1-AD5364D8B68A}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="9" max="9" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" t="str" cm="1">
-        <f t="array" ref="A1:A12">unit</f>
-        <v>Unit Price</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1">
-        <f>SUM(Discount)</f>
-        <v>38758</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>5675</v>
-      </c>
-      <c r="D2" t="e" vm="1">
-        <f>_xleta.DISC</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>3621</v>
-      </c>
-      <c r="D3" t="str" cm="1">
-        <f t="array" ref="D3:D15">Discount</f>
-        <v>Discount</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>2633</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Unit Price</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>2575</v>
-      </c>
-      <c r="D5">
-        <v>5675</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>4631</v>
-      </c>
-      <c r="D6">
-        <v>3621</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>3779</v>
-      </c>
-      <c r="D7">
-        <v>2633</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>5085</v>
-      </c>
-      <c r="D8">
-        <v>2575</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>4248</v>
-      </c>
-      <c r="D9">
-        <v>4631</v>
-      </c>
-      <c r="I9" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>1655</v>
-      </c>
-      <c r="D10">
-        <v>3779</v>
-      </c>
-      <c r="I10" t="s">
-        <v>0</v>
-      </c>
-      <c r="J10" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" t="s">
-        <v>2</v>
-      </c>
-      <c r="L10" t="s">
-        <v>4</v>
-      </c>
-      <c r="M10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>4856</v>
-      </c>
-      <c r="D11">
-        <v>5085</v>
-      </c>
-      <c r="I11">
-        <v>5675</v>
-      </c>
-      <c r="J11">
-        <v>10</v>
-      </c>
-      <c r="K11">
-        <f>I11*J11</f>
-        <v>56750</v>
-      </c>
-      <c r="L11" t="e">
-        <f>K11*$B$1</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M11" t="e">
-        <f>K11-L11</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>4248</v>
-      </c>
-      <c r="I12">
-        <v>3621</v>
-      </c>
-      <c r="J12">
-        <v>9</v>
-      </c>
-      <c r="K12">
-        <f t="shared" ref="K12:K20" si="0">I12*J12</f>
-        <v>32589</v>
-      </c>
-      <c r="L12" t="e">
-        <f t="shared" ref="L12:L21" si="1">K12*$B$1</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M12" t="e">
-        <f t="shared" ref="M12:M21" si="2">K12-L12</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="D13">
-        <v>1655</v>
-      </c>
-      <c r="I13">
-        <v>2633</v>
-      </c>
-      <c r="J13">
-        <v>7</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="0"/>
-        <v>18431</v>
-      </c>
-      <c r="L13" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M13" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="D14">
-        <v>4856</v>
-      </c>
-      <c r="I14">
-        <v>2575</v>
-      </c>
-      <c r="J14">
-        <v>10</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>25750</v>
-      </c>
-      <c r="L14" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M14" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>4631</v>
-      </c>
-      <c r="J15">
-        <v>5</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="0"/>
-        <v>23155</v>
-      </c>
-      <c r="L15" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M15" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="I16">
-        <v>3779</v>
-      </c>
-      <c r="J16">
-        <v>3</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="0"/>
-        <v>11337</v>
-      </c>
-      <c r="L16" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M16" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I17">
-        <v>5085</v>
-      </c>
-      <c r="J17">
-        <v>9</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="0"/>
-        <v>45765</v>
-      </c>
-      <c r="L17" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M17" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I18">
-        <v>4248</v>
-      </c>
-      <c r="J18">
-        <v>8</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="0"/>
-        <v>33984</v>
-      </c>
-      <c r="L18" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M18" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I19">
-        <v>1655</v>
-      </c>
-      <c r="J19">
-        <v>5</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="0"/>
-        <v>8275</v>
-      </c>
-      <c r="L19" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M19" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I20">
-        <v>4856</v>
-      </c>
-      <c r="J20">
-        <v>3</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="0"/>
-        <v>14568</v>
-      </c>
-      <c r="L20" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M20" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="J21" t="s">
-        <v>6</v>
-      </c>
-      <c r="K21">
-        <f>SUM(K11:K20)</f>
-        <v>270604</v>
-      </c>
-      <c r="L21" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M21" t="e">
-        <f t="shared" si="2"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -1737,135 +1355,381 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92FD34AD-8689-49B3-86CA-AA5A300AA926}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="7" max="7" width="13.81640625" customWidth="1"/>
+    <col min="9" max="9" width="10.1796875" customWidth="1"/>
+    <col min="11" max="11" width="11.08984375" customWidth="1"/>
+    <col min="15" max="15" width="10.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2">
+        <v>73472</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3">
+        <v>75489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4">
+        <v>75876</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5">
+        <v>64578</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="O6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="G7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="1"/>
+      <c r="O7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="O8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="O9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="G10" s="1">
+        <v>100</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="O10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="G11" s="1">
+        <v>101</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="2">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="G12" s="1">
+        <v>102</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="2">
+        <v>0.125</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="G13" s="1">
+        <v>103</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="2">
+        <v>0.16666666666666699</v>
+      </c>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="G14" s="1">
+        <v>104</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="2">
+        <v>0.20833333333333401</v>
+      </c>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="G15" s="1">
+        <v>105</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="G16" s="1">
+        <v>106</v>
+      </c>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="2">
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" spans="7:12" x14ac:dyDescent="0.35">
+      <c r="G17" s="1">
+        <v>107</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="2">
+        <v>0.33333333333333398</v>
+      </c>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+    </row>
+    <row r="18" spans="7:12" x14ac:dyDescent="0.35">
+      <c r="G18" s="1">
+        <v>108</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" spans="7:12" x14ac:dyDescent="0.35">
+      <c r="G19" s="1">
+        <v>109</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="2">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" spans="7:12" x14ac:dyDescent="0.35">
+      <c r="G20" s="1">
+        <v>110</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="2">
+        <v>0.45833333333333398</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+    </row>
+    <row r="21" spans="7:12" x14ac:dyDescent="0.35">
+      <c r="G21" s="1">
+        <v>111</v>
+      </c>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+    </row>
+    <row r="22" spans="7:12" x14ac:dyDescent="0.35">
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="2">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+    </row>
+  </sheetData>
+  <dataValidations count="7">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7" xr:uid="{2D5F4F18-60F5-4108-B303-3D02BF2C3B4C}">
+      <formula1>1</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7:I22" xr:uid="{94844C7C-D8EE-4B92-8171-B61C1E47BA7C}">
+      <formula1>5</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation type="time" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J7" xr:uid="{AC473344-CE6B-42AD-938E-8F89601DD3DF}">
+      <formula1>0</formula1>
+      <formula2>0.5</formula2>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="GET LOST!!" error="YOU ARE NOT ACCURATE!!" promptTitle="list" prompt="Kindly be accurate" sqref="K7" xr:uid="{A37CC2F9-1030-47CE-8F3E-172FE1DE5912}">
+      <formula1>$O$7:$O$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K8:K22" xr:uid="{318BD15D-74F7-4BA1-9D26-B60FD6D7359D}">
+      <formula1>$O$7:$O$10</formula1>
+    </dataValidation>
+    <dataValidation type="whole" showInputMessage="1" showErrorMessage="1" sqref="G8:G22" xr:uid="{DC04C113-6B7B-44D0-8E11-43392EC2096B}">
+      <formula1>1</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="time" showInputMessage="1" showErrorMessage="1" sqref="J8:J22" xr:uid="{713D4176-5B5F-464F-9F74-A57652CB1FA0}">
+      <formula1>0</formula1>
+      <formula2>0.5</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F27DB98-E71A-4192-AE5A-E90A0877F9EA}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2">
-        <v>739</v>
-      </c>
-      <c r="C2">
-        <v>324</v>
-      </c>
-      <c r="D2">
-        <v>2414</v>
-      </c>
-      <c r="E2">
-        <v>5457</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3">
-        <v>678</v>
-      </c>
-      <c r="C3">
-        <v>8887</v>
-      </c>
-      <c r="D3">
-        <v>8920</v>
-      </c>
-      <c r="E3">
-        <v>4358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4">
-        <v>432</v>
-      </c>
-      <c r="C4">
-        <v>5776</v>
-      </c>
-      <c r="D4">
-        <v>3457</v>
-      </c>
-      <c r="E4">
-        <v>9654</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5">
-        <v>544</v>
-      </c>
-      <c r="C5">
-        <v>6567</v>
-      </c>
-      <c r="D5">
-        <v>4567</v>
-      </c>
-      <c r="E5">
-        <v>7898</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3BF5335-0734-43BC-9D9B-F2FE4578C1B3}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
     <col min="9" max="9" width="10.453125" customWidth="1"/>
+    <col min="14" max="14" width="13.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>19</v>
       </c>
       <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>27</v>
       </c>
       <c r="B2">
         <v>739</v>
@@ -1880,9 +1744,9 @@
         <v>5457</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>678</v>
@@ -1891,18 +1755,18 @@
         <v>8887</v>
       </c>
       <c r="D3">
-        <v>8920</v>
+        <v>-8920</v>
       </c>
       <c r="E3">
         <v>4358</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>432</v>
+        <v>-432</v>
       </c>
       <c r="C4">
         <v>5776</v>
@@ -1914,9 +1778,9 @@
         <v>9654</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>544</v>
@@ -1932,6 +1796,42 @@
       </c>
       <c r="I5" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="L12" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="L13" t="e">
+        <f>FIND(N13," "+2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="L14">
+        <f>LEN(N14)</f>
+        <v>8</v>
+      </c>
+      <c r="N14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N16" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1940,10 +1840,136 @@
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
+      <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{3D21986C-8797-4A81-9E8F-C7DA7B93B04A}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet6!E2</xm:f>
+              <xm:sqref>F1</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup type="stacked" displayEmptyCellsAs="gap" xr2:uid="{B3E1F14C-F792-4F7D-9CC1-D4E713D7FE62}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet6!B2:E2</xm:f>
+              <xm:sqref>F2</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet6!C2:F2</xm:f>
+              <xm:sqref>G2</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet6!D2:G2</xm:f>
+              <xm:sqref>H2</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{3C92F3E4-06C5-4B00-A8F5-FD807154A3D0}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet6!B3:E3</xm:f>
+              <xm:sqref>F3</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{5F0CB77E-6A53-4E29-841A-2721607BCB2E}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet6!B4:E4</xm:f>
+              <xm:sqref>F4</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{967882D3-678A-4F54-B1E4-F3595182D7A6}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet6!B5:E5</xm:f>
+              <xm:sqref>F5</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup type="column" displayEmptyCellsAs="gap" xr2:uid="{71F1230E-06F4-42A9-9FF7-5C3B5058284B}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet6!G3</xm:f>
+              <xm:sqref>E6</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup type="column" displayEmptyCellsAs="gap" xr2:uid="{22D14F60-6F30-4E9B-9C32-892450C9AC8E}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet6!B3:E3</xm:f>
+              <xm:sqref>G3</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+      </x14:sparklineGroups>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF7552E3-18B2-4F4F-8898-31232630D347}">
   <dimension ref="A1:R48"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="3" x14ac:dyDescent="0.35"/>
@@ -1956,34 +1982,34 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="2" spans="1:18" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B2">
-        <f>Sheet3!$B$2</f>
-        <v>739</v>
-      </c>
-      <c r="C2">
-        <f>Sheet3!$C$2</f>
-        <v>324</v>
-      </c>
-      <c r="D2">
-        <f>Sheet3!$D$2</f>
-        <v>2414</v>
-      </c>
-      <c r="E2">
-        <f>Sheet3!$E$2</f>
-        <v>5457</v>
+      <c r="B2" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C2" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D2" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E2" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="3" spans="1:18" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35">
@@ -2006,41 +2032,41 @@
     </row>
     <row r="4" spans="1:18" collapsed="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4">
+        <v>26</v>
+      </c>
+      <c r="B4" t="e">
         <f>SUM(B2:B3)</f>
-        <v>1478</v>
-      </c>
-      <c r="C4">
+        <v>#REF!</v>
+      </c>
+      <c r="C4" t="e">
         <f>SUM(C2:C3)</f>
-        <v>648</v>
-      </c>
-      <c r="D4">
+        <v>#REF!</v>
+      </c>
+      <c r="D4" t="e">
         <f>SUM(D2:D3)</f>
-        <v>4828</v>
-      </c>
-      <c r="E4">
+        <v>#REF!</v>
+      </c>
+      <c r="E4" t="e">
         <f>SUM(E2:E3)</f>
-        <v>10914</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="5" spans="1:18" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B5">
-        <f>Sheet3!$B$3</f>
-        <v>678</v>
-      </c>
-      <c r="C5">
-        <f>Sheet3!$C$3</f>
-        <v>8887</v>
-      </c>
-      <c r="D5">
-        <f>Sheet3!$D$3</f>
-        <v>8920</v>
-      </c>
-      <c r="E5">
-        <f>Sheet3!$E$3</f>
-        <v>4358</v>
+      <c r="B5" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C5" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D5" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E5" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="6" spans="1:18" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35">
@@ -2054,7 +2080,7 @@
       </c>
       <c r="D6">
         <f>Sheet6!$D$3</f>
-        <v>8920</v>
+        <v>-8920</v>
       </c>
       <c r="E6">
         <f>Sheet6!$E$3</f>
@@ -2063,47 +2089,47 @@
     </row>
     <row r="7" spans="1:18" collapsed="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7">
+        <v>27</v>
+      </c>
+      <c r="B7" t="e">
         <f>SUM(B5:B6)</f>
-        <v>1356</v>
-      </c>
-      <c r="C7">
+        <v>#REF!</v>
+      </c>
+      <c r="C7" t="e">
         <f>SUM(C5:C6)</f>
-        <v>17774</v>
-      </c>
-      <c r="D7">
+        <v>#REF!</v>
+      </c>
+      <c r="D7" t="e">
         <f>SUM(D5:D6)</f>
-        <v>17840</v>
-      </c>
-      <c r="E7">
+        <v>#REF!</v>
+      </c>
+      <c r="E7" t="e">
         <f>SUM(E5:E6)</f>
-        <v>8716</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="8" spans="1:18" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B8">
-        <f>Sheet3!$B$4</f>
-        <v>432</v>
-      </c>
-      <c r="C8">
-        <f>Sheet3!$C$4</f>
-        <v>5776</v>
-      </c>
-      <c r="D8">
-        <f>Sheet3!$D$4</f>
-        <v>3457</v>
-      </c>
-      <c r="E8">
-        <f>Sheet3!$E$4</f>
-        <v>9654</v>
+      <c r="B8" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C8" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D8" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E8" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="9" spans="1:18" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35">
       <c r="B9">
         <f>Sheet6!$B$4</f>
-        <v>432</v>
+        <v>-432</v>
       </c>
       <c r="C9">
         <f>Sheet6!$C$4</f>
@@ -2120,41 +2146,41 @@
     </row>
     <row r="10" spans="1:18" collapsed="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10">
+        <v>28</v>
+      </c>
+      <c r="B10" t="e">
         <f>SUM(B8:B9)</f>
-        <v>864</v>
-      </c>
-      <c r="C10">
+        <v>#REF!</v>
+      </c>
+      <c r="C10" t="e">
         <f>SUM(C8:C9)</f>
-        <v>11552</v>
-      </c>
-      <c r="D10">
+        <v>#REF!</v>
+      </c>
+      <c r="D10" t="e">
         <f>SUM(D8:D9)</f>
-        <v>6914</v>
-      </c>
-      <c r="E10">
+        <v>#REF!</v>
+      </c>
+      <c r="E10" t="e">
         <f>SUM(E8:E9)</f>
-        <v>19308</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="11" spans="1:18" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B11">
-        <f>Sheet3!$B$5</f>
-        <v>544</v>
-      </c>
-      <c r="C11">
-        <f>Sheet3!$C$5</f>
-        <v>6567</v>
-      </c>
-      <c r="D11">
-        <f>Sheet3!$D$5</f>
-        <v>4567</v>
-      </c>
-      <c r="E11">
-        <f>Sheet3!$E$5</f>
-        <v>7898</v>
+      <c r="B11" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C11" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D11" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E11" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="12" spans="1:18" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35">
@@ -2177,23 +2203,23 @@
     </row>
     <row r="13" spans="1:18" collapsed="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13">
+        <v>29</v>
+      </c>
+      <c r="B13" t="e">
         <f>SUM(B11:B12)</f>
-        <v>1088</v>
-      </c>
-      <c r="C13">
+        <v>#REF!</v>
+      </c>
+      <c r="C13" t="e">
         <f>SUM(C11:C12)</f>
-        <v>13134</v>
-      </c>
-      <c r="D13">
+        <v>#REF!</v>
+      </c>
+      <c r="D13" t="e">
         <f>SUM(D11:D12)</f>
-        <v>9134</v>
-      </c>
-      <c r="E13">
+        <v>#REF!</v>
+      </c>
+      <c r="E13" t="e">
         <f>SUM(E11:E12)</f>
-        <v>15796</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
@@ -2207,15 +2233,15 @@
         <v>21</v>
       </c>
       <c r="Q16" t="s">
+        <v>30</v>
+      </c>
+      <c r="R16" t="s">
         <v>31</v>
-      </c>
-      <c r="R16" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="21" spans="6:18" hidden="1" outlineLevel="3" x14ac:dyDescent="0.35">
       <c r="F21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G21">
         <v>432</v>
@@ -2226,21 +2252,21 @@
       <c r="I21">
         <v>3457</v>
       </c>
-      <c r="J21">
-        <f>Sheet3!$B$2</f>
-        <v>739</v>
-      </c>
-      <c r="K21">
-        <f>Sheet3!$C$2</f>
-        <v>324</v>
-      </c>
-      <c r="L21">
-        <f>Sheet3!$D$2</f>
-        <v>2414</v>
-      </c>
-      <c r="M21">
-        <f>Sheet3!$E$2</f>
-        <v>5457</v>
+      <c r="J21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M21" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="O21">
         <v>544</v>
@@ -2257,7 +2283,7 @@
     </row>
     <row r="22" spans="6:18" hidden="1" outlineLevel="3" collapsed="1" x14ac:dyDescent="0.35">
       <c r="F22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G22">
         <v>544</v>
@@ -2286,39 +2312,39 @@
       </c>
     </row>
     <row r="23" spans="6:18" hidden="1" outlineLevel="2" collapsed="1" x14ac:dyDescent="0.35">
-      <c r="J23">
+      <c r="J23" t="e">
         <f>AVERAGE(J21:J22)</f>
-        <v>739</v>
-      </c>
-      <c r="K23">
+        <v>#REF!</v>
+      </c>
+      <c r="K23" t="e">
         <f>AVERAGE(K21:K22)</f>
-        <v>324</v>
-      </c>
-      <c r="L23">
+        <v>#REF!</v>
+      </c>
+      <c r="L23" t="e">
         <f>AVERAGE(L21:L22)</f>
-        <v>2414</v>
-      </c>
-      <c r="M23">
+        <v>#REF!</v>
+      </c>
+      <c r="M23" t="e">
         <f>AVERAGE(M21:M22)</f>
-        <v>5457</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="24" spans="6:18" hidden="1" outlineLevel="3" x14ac:dyDescent="0.35">
-      <c r="J24">
-        <f>Sheet3!$B$3</f>
-        <v>678</v>
-      </c>
-      <c r="K24">
-        <f>Sheet3!$C$3</f>
-        <v>8887</v>
-      </c>
-      <c r="L24">
-        <f>Sheet3!$D$3</f>
-        <v>8920</v>
-      </c>
-      <c r="M24">
-        <f>Sheet3!$E$3</f>
-        <v>4358</v>
+      <c r="J24" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K24" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L24" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M24" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="25" spans="6:18" hidden="1" outlineLevel="3" collapsed="1" x14ac:dyDescent="0.35">
@@ -2332,7 +2358,7 @@
       </c>
       <c r="L25">
         <f>Sheet6!$D$3</f>
-        <v>8920</v>
+        <v>-8920</v>
       </c>
       <c r="M25">
         <f>Sheet6!$E$3</f>
@@ -2340,45 +2366,45 @@
       </c>
     </row>
     <row r="26" spans="6:18" hidden="1" outlineLevel="2" collapsed="1" x14ac:dyDescent="0.35">
-      <c r="J26">
+      <c r="J26" t="e">
         <f>AVERAGE(J24:J25)</f>
-        <v>678</v>
-      </c>
-      <c r="K26">
+        <v>#REF!</v>
+      </c>
+      <c r="K26" t="e">
         <f>AVERAGE(K24:K25)</f>
-        <v>8887</v>
-      </c>
-      <c r="L26">
+        <v>#REF!</v>
+      </c>
+      <c r="L26" t="e">
         <f>AVERAGE(L24:L25)</f>
-        <v>8920</v>
-      </c>
-      <c r="M26">
+        <v>#REF!</v>
+      </c>
+      <c r="M26" t="e">
         <f>AVERAGE(M24:M25)</f>
-        <v>4358</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="27" spans="6:18" hidden="1" outlineLevel="3" x14ac:dyDescent="0.35">
-      <c r="J27">
-        <f>Sheet3!$B$4</f>
-        <v>432</v>
-      </c>
-      <c r="K27">
-        <f>Sheet3!$C$4</f>
-        <v>5776</v>
-      </c>
-      <c r="L27">
-        <f>Sheet3!$D$4</f>
-        <v>3457</v>
-      </c>
-      <c r="M27">
-        <f>Sheet3!$E$4</f>
-        <v>9654</v>
+      <c r="J27" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K27" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L27" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M27" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="28" spans="6:18" hidden="1" outlineLevel="3" x14ac:dyDescent="0.35">
       <c r="J28">
         <f>Sheet6!$B$4</f>
-        <v>432</v>
+        <v>-432</v>
       </c>
       <c r="K28">
         <f>Sheet6!$C$4</f>
@@ -2394,39 +2420,39 @@
       </c>
     </row>
     <row r="29" spans="6:18" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35">
-      <c r="J29">
+      <c r="J29" t="e">
         <f>AVERAGE(J27:J28)</f>
-        <v>432</v>
-      </c>
-      <c r="K29">
+        <v>#REF!</v>
+      </c>
+      <c r="K29" t="e">
         <f>AVERAGE(K27:K28)</f>
-        <v>5776</v>
-      </c>
-      <c r="L29">
+        <v>#REF!</v>
+      </c>
+      <c r="L29" t="e">
         <f>AVERAGE(L27:L28)</f>
-        <v>3457</v>
-      </c>
-      <c r="M29">
+        <v>#REF!</v>
+      </c>
+      <c r="M29" t="e">
         <f>AVERAGE(M27:M28)</f>
-        <v>9654</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="30" spans="6:18" hidden="1" outlineLevel="3" x14ac:dyDescent="0.35">
-      <c r="J30">
-        <f>Sheet3!$B$5</f>
-        <v>544</v>
-      </c>
-      <c r="K30">
-        <f>Sheet3!$C$5</f>
-        <v>6567</v>
-      </c>
-      <c r="L30">
-        <f>Sheet3!$D$5</f>
-        <v>4567</v>
-      </c>
-      <c r="M30">
-        <f>Sheet3!$E$5</f>
-        <v>7898</v>
+      <c r="J30" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K30" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L30" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="M30" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="31" spans="6:18" hidden="1" outlineLevel="3" x14ac:dyDescent="0.35">
@@ -2448,21 +2474,21 @@
       </c>
     </row>
     <row r="32" spans="6:18" hidden="1" outlineLevel="2" x14ac:dyDescent="0.35">
-      <c r="J32">
+      <c r="J32" t="e">
         <f>AVERAGE(J30:J31)</f>
-        <v>544</v>
-      </c>
-      <c r="K32">
+        <v>#REF!</v>
+      </c>
+      <c r="K32" t="e">
         <f>AVERAGE(K30:K31)</f>
-        <v>6567</v>
-      </c>
-      <c r="L32">
+        <v>#REF!</v>
+      </c>
+      <c r="L32" t="e">
         <f>AVERAGE(L30:L31)</f>
-        <v>4567</v>
-      </c>
-      <c r="M32">
+        <v>#REF!</v>
+      </c>
+      <c r="M32" t="e">
         <f>AVERAGE(M30:M31)</f>
-        <v>7898</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="33" spans="5:9" hidden="1" outlineLevel="2" collapsed="1" x14ac:dyDescent="0.35"/>
@@ -2472,7 +2498,7 @@
     <row r="37" spans="5:9" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="38" spans="5:9" hidden="1" outlineLevel="2" x14ac:dyDescent="0.35">
       <c r="E38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F38">
         <v>985.33333333333337</v>
@@ -2489,7 +2515,7 @@
     </row>
     <row r="39" spans="5:9" hidden="1" outlineLevel="2" collapsed="1" x14ac:dyDescent="0.35">
       <c r="E39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F39">
         <v>678</v>
@@ -2506,7 +2532,7 @@
     </row>
     <row r="40" spans="5:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="E40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F40">
         <v>432</v>
@@ -2523,7 +2549,7 @@
     </row>
     <row r="41" spans="5:9" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35">
       <c r="E41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F41">
         <v>544</v>
@@ -2546,7 +2572,7 @@
     <row r="47" spans="5:9" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="48" spans="5:9" collapsed="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <dataConsolidate function="average" leftLabels="1" topLabels="1">
+  <dataConsolidate function="average" topLabels="1">
     <dataRefs count="3">
       <dataRef ref="A1:E5" sheet="consolidate"/>
       <dataRef ref="A1:E5" sheet="Sheet3"/>
